--- a/naver-place-crawler/results_health/달성군_헬스장.xlsx
+++ b/naver-place-crawler/results_health/달성군_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>플레이짐&amp;PT 현풍점</t>
+          <t>포에버 짐 화원점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>playgym_hp@naver.com</t>
+          <t>4evergym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1484-0679</t>
+          <t>0507-1307-6093</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 34 601, 604호</t>
+          <t>대구광역시 달성군 화원읍 성화로4길 11 2층,3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/playgym_hp</t>
+          <t>https://blog.naver.com/4evergym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>224</v>
+        <v>178</v>
       </c>
       <c r="Q2" t="n">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="R2" t="n">
-        <v>388</v>
+        <v>233</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1567754721</t>
+          <t>1747875122</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1567754721</t>
+          <t>https://m.place.naver.com/place/1747875122</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>플레이짐&amp;Pt현풍유가점</t>
+          <t>짐 아틀라스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kingfitnessgym@naver.com</t>
+          <t>gym_atlas@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>053-617-4705</t>
+          <t>0507-1339-0135</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노공원로 65 5층 플레이&amp;PT 현풍유가점</t>
+          <t>대구광역시 달성군 가창면 가창로 1122 지하 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/king_korea_2021</t>
+          <t>https://blog.naver.com/gym_atlas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>426</v>
+        <v>125</v>
       </c>
       <c r="R3" t="n">
-        <v>646</v>
+        <v>155</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1614066731</t>
+          <t>36520319</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614066731</t>
+          <t>https://m.place.naver.com/place/36520319</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -752,25 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헬스브로짐&amp;PT 대실역점</t>
+          <t>세천스파헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>paradise_is@naver.com</t>
+          <t>schealth_spa@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1429-1180</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 859 8층</t>
+          <t>대구광역시 달성군 다사읍 세천로 108 5층 헬스장</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/health_brogym_daesil</t>
+          <t>https://www.instagram.com/tailorgym_secheonspa/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>234</v>
+        <v>115</v>
       </c>
       <c r="Q4" t="n">
-        <v>287</v>
+        <v>81</v>
       </c>
       <c r="R4" t="n">
-        <v>521</v>
+        <v>196</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1736955282</t>
+          <t>2062944785</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1736955282</t>
+          <t>https://m.place.naver.com/place/2062944785</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JJ짐 다사 대실역점 헬스 PT</t>
+          <t>동아짐 헬스&amp;PT 현풍점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sjk2948@naver.com</t>
+          <t>dong_a_gym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1329-4566</t>
+          <t>0507-1391-7710</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 873 5층</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로 243 401호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sjk2948</t>
+          <t>https://blog.naver.com/dong_a_gym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>252</v>
+        <v>42</v>
       </c>
       <c r="Q5" t="n">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
-        <v>408</v>
+        <v>69</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1377099587</t>
+          <t>2031706267</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377099587</t>
+          <t>https://m.place.naver.com/place/2031706267</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -936,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>뷰티니스짐 현풍테크노점</t>
+          <t>한샘사우나헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>technogym1@naver.com</t>
+          <t>dutmdgns0402@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1411-9684</t>
+          <t>053-551-8888</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로 254 9층</t>
+          <t>대구광역시 달성군 화원읍 명천로 257</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/technogym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -968,12 +972,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -989,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>854</v>
+        <v>72</v>
       </c>
       <c r="Q6" t="n">
-        <v>1127</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>1981</v>
+        <v>79</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>38648253</t>
+          <t>16131730</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648253</t>
+          <t>https://m.place.naver.com/place/16131730</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>패러다임짐 PT 현풍테크노점</t>
+          <t>망고짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>paradigm999@naver.com</t>
+          <t>mango_gym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1484-7281</t>
+          <t>0507-1326-6177</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노공원로 59 4층, 패러다임짐 현풍테크노점</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 52 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/paradigmgym_hp</t>
+          <t>https://www.instagram.com/mang.go55?igsh=cmtuc3ltY3R5dnpq</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="R7" t="n">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1296586077</t>
+          <t>1899621515</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296586077</t>
+          <t>https://m.place.naver.com/place/1899621515</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1124,39 +1128,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>053짐 대실역점 헬스&amp;PT</t>
+          <t>그린월드헬스클럽</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>shutupsquat@naver.com</t>
+          <t>hunkyle0104@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1347-0243</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로1길 29-9 2층</t>
+          <t>대구광역시 달성군 화원읍 비슬로530길 29-15</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_RTxeHs/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1172,22 +1172,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>377</v>
+        <v>2</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1050863472</t>
+          <t>16206947</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050863472</t>
+          <t>https://m.place.naver.com/place/16206947</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>여성 맞춤형 헬스&amp;PT 비벨라핏 다사 대실역점</t>
+          <t>패러다임짐 PT 현풍테크노점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>doldol5311573@naver.com</t>
+          <t>paradigm999@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1353-5294</t>
+          <t>0507-1484-7281</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 880 대실빌딩 3층 여성전용피트니스 비벨라핏 다사점</t>
+          <t>대구광역시 달성군 유가읍 테크노공원로 59 4층, 패러다임짐 현풍테크노점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/b.bellafit_daesil/</t>
+          <t>https://www.instagram.com/paradigmgym_hp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>476</v>
+        <v>89</v>
       </c>
       <c r="Q9" t="n">
-        <v>346</v>
+        <v>145</v>
       </c>
       <c r="R9" t="n">
-        <v>822</v>
+        <v>234</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,56 +1290,52 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1548249227</t>
+          <t>1296586077</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548249227</t>
+          <t>https://m.place.naver.com/place/1296586077</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐플릭스 대실역점</t>
+          <t>헬스브로짐&amp;PT 대실역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>qo6107@naver.com</t>
+          <t>key_happy@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1363-2799</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 863 5층</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 859 8층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr</t>
+          <t>https://www.instagram.com/health_brogym_daesil</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1369,32 +1365,6176 @@
         </is>
       </c>
       <c r="P10" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>288</v>
+      </c>
+      <c r="R10" t="n">
+        <v>523</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1736955282</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1736955282</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>스마일피티</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lionajing@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1387-9314</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 달구벌대로 866 C&amp;B타워 6층 스마일피티</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/smilept_cap/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>24</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1546368872</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1546368872</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>동아헬스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>kht8kht@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 논공읍 논공로 749 6층 동아헬스</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>12</v>
+      </c>
+      <c r="R12" t="n">
+        <v>24</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1706569605</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1706569605</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>와이짐 구지점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gym-y3@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1403-9903</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 구지면 국가산단대로42길 5-23 6층 와이짐 구지점</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gym-y3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>76</v>
+      </c>
+      <c r="R13" t="n">
+        <v>109</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1037912613</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1037912613</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>세천케어짐PT샵</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>caregym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1349-6648</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 세천북로 7 4층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/caregym_</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>150</v>
+      </c>
+      <c r="R14" t="n">
+        <v>307</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1858573540</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1858573540</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>여성전용 그룹PT 크롭핏 다사점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gnstjqdl1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1366-4795</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 대실역북로1길 5-1 죽곡메디힐빌딩 7층 여성전용 그룹PT 크롭핏</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gnstjqdl1234</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>225</v>
+      </c>
+      <c r="R15" t="n">
+        <v>515</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1403050690</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1403050690</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>더바디스쿨 화원점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>thebodyschool_hwawon@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>053-635-0812</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 화원읍 비슬로 2616</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thebodyschool_hwawon</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>17</v>
+      </c>
+      <c r="R16" t="n">
+        <v>82</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1939140331</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1939140331</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>레드짐 현풍점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>redgym114@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1437-2268</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 26 8층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redgym_fit</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>307</v>
+      </c>
+      <c r="R17" t="n">
+        <v>572</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1621391509</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1621391509</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>호석</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ydy5061@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 세천로 108</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1465682374</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1465682374</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>reset20 EMS studio</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>rugbyyy07@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1427-0322</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 화원읍 성화로 14</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>118041027</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/118041027</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>피트온24 중동점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>fiton24_jd@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1395-8629</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>대구광역시 수성구 수성로 212 광원빌딩 3층 피트온24 중동점</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fiton24_jd</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1620</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>785</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2405</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1472735445</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1472735445</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>053짐 대실역점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>shutupsquat@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1347-0243</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 대실역북로1길 29-9 2층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_RTxeHs/chat</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>166</v>
+      </c>
+      <c r="R21" t="n">
+        <v>378</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1050863472</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1050863472</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>뷰티니스짐 현풍테크노점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>technogym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1411-9684</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로 254 9층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/technogym1</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>858</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1128</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1986</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>38648253</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38648253</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스용품</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>제이에스헬스케어</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jshealth0312@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 현풍읍 비슬로 644 제이에스헬스케어</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/cwheallthcare</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>126</v>
+      </c>
+      <c r="R23" t="n">
+        <v>130</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1947032802</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1947032802</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>제이에스짐앤스파</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jsgym2020@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1338-5512</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 현풍읍 현풍중앙로14길 71 제이에스짐앤스파</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jsgym2020</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>332</v>
+      </c>
+      <c r="R24" t="n">
+        <v>380</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1249711626</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1249711626</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>다짐휘트니스 대곡점/1:1PT/GX수업/운동프로그램지도</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dagym_daegok@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>053-634-1414</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 화원읍 비슬로 2727 4층 다짐휘트니스</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dagym_daegok</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>558</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>27</v>
+      </c>
+      <c r="R25" t="n">
+        <v>585</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>37989679</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37989679</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>스톤짐 남산점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>nb99022@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>053-424-4001</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>대구광역시 중구 달구벌대로 2012 13층 (11, 13, 14층)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stonegym_namsan</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>86</v>
+      </c>
+      <c r="R26" t="n">
+        <v>376</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2027766732</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2027766732</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>피트온24 범어점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>fiton24_beomeo@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>053-759-3166</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>대구광역시 수성구 범어천로 214 더리브 503-507호</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fiton24_beomeo</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>2339</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>986</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3325</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1328042225</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1328042225</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>플레이짐&amp;PT 현풍점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>playgym_hp@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1484-0679</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 34 601, 604호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/playgym_hp</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>163</v>
+      </c>
+      <c r="R28" t="n">
+        <v>387</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1567754721</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1567754721</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>여성 맞춤형 헬스&amp;PT 비벨라핏 다사 대실역점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>doldol5311573@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1353-5294</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 달구벌대로 880 대실빌딩 3층 여성전용피트니스 비벨라핏 다사점</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/b.bellafit_daesil/</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>475</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>350</v>
+      </c>
+      <c r="R29" t="n">
+        <v>825</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1548249227</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1548249227</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>레드짐 서재점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>redgym_seojae@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1338-2445</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 서재로 31 3~4층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/redgym_seojae</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>107</v>
+      </c>
+      <c r="R30" t="n">
+        <v>229</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2048462768</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2048462768</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>행복마당</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>happyseogu@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 68</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1846649632</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1846649632</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>웰휘트니스24h 다사서재점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>tjql23@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1347-9665</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 서재로 121 4층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tjql23</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>55</v>
+      </c>
+      <c r="R32" t="n">
+        <v>132</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1161171342</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1161171342</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>다빠짐&amp;죠아짐</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>joagym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1472-6488</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 15 명륜진사갈비 3층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/joagym1</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>135</v>
+      </c>
+      <c r="R33" t="n">
+        <v>143</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1468896867</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1468896867</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>레드짐 현풍2호점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>defertoneminem@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1431-2318</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 유가읍 테크노상업로4길 17-9 3층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redgym_yg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>305</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>229</v>
+      </c>
+      <c r="R34" t="n">
+        <v>534</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1274922467</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1274922467</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JJ짐 다사 대실역점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>sjk2948@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1329-4566</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 달구벌대로 873 5층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sjk2948</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
         <v>252</v>
       </c>
-      <c r="Q10" t="n">
-        <v>607</v>
-      </c>
-      <c r="R10" t="n">
-        <v>859</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="Q35" t="n">
+        <v>154</v>
+      </c>
+      <c r="R35" t="n">
+        <v>406</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1377099587</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1377099587</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>헬스위드짐</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>hjya0119@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1309-5393</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 유가읍 테크노상업로4길 17-9 4층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hjya0119</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>124</v>
+      </c>
+      <c r="R36" t="n">
+        <v>134</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1700394540</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1700394540</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>바디컷피티샵 현풍</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bodycut-@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1357-3856</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 34 1동 3층 301호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodycut-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>259</v>
+      </c>
+      <c r="R37" t="n">
+        <v>314</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1642240188</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1642240188</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>선샤인 사우나 헬스</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>yoon766@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>053-587-0035</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 대실역북로2길 8-6</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>310</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>38415528</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38415528</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>플레이짐&amp;Pt현풍유가점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>kingfitnessgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>053-617-4705</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 유가읍 테크노공원로 65 5층 플레이&amp;PT 현풍유가점</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/king_korea_2021</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>426</v>
+      </c>
+      <c r="R39" t="n">
+        <v>645</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1614066731</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614066731</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>피크짐 화원점 헬스 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>peakgym2022@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1446-6339</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 화원읍 사문진로 441 4층, 5층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://litt.ly/peakgym</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>23</v>
+      </c>
+      <c r="R40" t="n">
+        <v>100</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1304504873</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1304504873</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>디젤피트니스</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>dieseldaegok@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1303-0976</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 옥포읍 돌미상업로1길 2 화인탑메디컬빌딩 7층 디젤피트니스</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>241</v>
+      </c>
+      <c r="R41" t="n">
+        <v>391</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1888886298</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1888886298</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>새롬사우나 헬스</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>053-638-4386</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 화원읍 비슬로 2508</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>4</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>16130959</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16130959</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>서재헬스</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>seojaehealth@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 서재로 141 서재헬스</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seojaehealth</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>7</v>
+      </c>
+      <c r="R43" t="n">
+        <v>18</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1159781373</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1159781373</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>귀빈헬스</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dy0655@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>053-593-2555</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 대실역북로 9 7층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>35</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>21311111</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21311111</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>GO GYM 구지점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>gogym3334@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1436-3497</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 구지면 과학마을로4길 7-2 2층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gogym3334</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>41</v>
+      </c>
+      <c r="R45" t="n">
+        <v>41</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1444367346</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1444367346</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>바디엔지니어스짐 헬스&amp;PT 수성점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>chl3503@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1491-7677</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>대구광역시 수성구 청수로26길 36 한성스퀘어 5층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://boddy.imweb.me/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>945</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1344</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2289</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1885094891</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1885094891</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>크로스핏 이공</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>crossfit20tr@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1322-5663</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 다사로4길 8 크로스핏20</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfit20tr/</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>123</v>
+      </c>
+      <c r="R47" t="n">
+        <v>133</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1615243167</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1615243167</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AGYM헬스</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>agym_11@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 구지면 과학마을로5길 35</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1906219799</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1906219799</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>테크노폴리스화성파크드림피트니스센터</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>anheesang1985@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 유가읍 테크노북로 165</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>818202311</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/818202311</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>공유누리 개방자원</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>다사읍주민자치센터 본관2층(헬스장)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ulju_love@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 매곡로12길 37 다사읍주민자치센터 본관2층 헬스장</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1824150538</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1824150538</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>비슬산게르마늄스파</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bsm5055@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>053-566-5000</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 유가읍 테크노순환로12길 4</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bsm5055</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>228</v>
+      </c>
+      <c r="R51" t="n">
+        <v>417</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>488162588</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/488162588</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>짐 엘리트 대실역점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gym_b@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1417-4477</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 달구벌대로 874 A동 3층 짐 엘리트 대실역점</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gym_b/224238759740</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>269</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>423</v>
+      </c>
+      <c r="R52" t="n">
+        <v>692</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>520470643</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/520470643</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>atmhjqnib@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1341-2034</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>대구광역시 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/atmhjqnib</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>1193</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>558</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1751</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>671730517</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/671730517</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>나우휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>kns3791@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>053-614-0255</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 논공읍 논공로5길 229</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>16135809</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16135809</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>더디어짐 헬스&amp;PT 현풍점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>the_deergym@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1390-9558</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 48 10층 1001호, 1002호, 1003호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://thedeargym.homebuilder.co.kr/</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>282</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>123</v>
+      </c>
+      <c r="R55" t="n">
+        <v>405</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1844851101</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1844851101</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>옥포서한이다음휘트니스센터</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 옥포읍 돌미로6길 5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3</v>
+      </c>
+      <c r="R56" t="n">
+        <v>3</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1480559305</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1480559305</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>파워헬스클럽</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>power2963805@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 화원읍 비슬로 2697</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>5</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1475412010</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1475412010</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>부속건물</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>달성군여성문화복지센터수영헬스장</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>radman99@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 화원읍 성천로 5</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>33</v>
+      </c>
+      <c r="R58" t="n">
+        <v>33</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>19637848</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19637848</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>패러다임짐 헬스&amp;PT 다사서재점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>paradigm22@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1446-8272</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 서재로 144 2층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/paradigm22</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>110</v>
+      </c>
+      <c r="R59" t="n">
+        <v>201</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1848019910</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1848019910</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>현풍 하이그룹피티 &amp; 찌지다</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1347-3429</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 50 제이앤비빌딩 5층 501호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/invites/contact/?i=1amokd5vtp2ir&amp;utm_content=mvgw8cs</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>140</v>
+      </c>
+      <c r="R60" t="n">
+        <v>175</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1807496277</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1807496277</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>다이어트,비만</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>예스점핑다이어트</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>mamihong@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 다사역로 5 4층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/yes.jumping</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>50</v>
+      </c>
+      <c r="R61" t="n">
+        <v>52</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1206224366</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1206224366</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>에프엠트레이닝센터</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>fm_trainingcenter@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 유가읍 테크노순환로7길 33 1층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fm_trainingcenter</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>24</v>
+      </c>
+      <c r="R62" t="n">
+        <v>84</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1843484347</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1843484347</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>크라이오식스</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>tjwls1986@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 화원읍 성화로 14 2F</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/cryosix_6</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>6</v>
+      </c>
+      <c r="R63" t="n">
+        <v>8</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1375896553</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1375896553</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>에이짐휘트니스</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>agymf@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1320-5959</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 구지면 과학마을로5길 35 드림랜드 1층 101호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>7</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1554834015</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1554834015</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>라라그룹피티</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>top85601@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1400-0326</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 대실역남로 18 3층 304호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lala_pt0303</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>53</v>
+      </c>
+      <c r="R65" t="n">
+        <v>65</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1435201471</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1435201471</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>짐플릭스 대실역점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>qo6107@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1363-2799</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 달구벌대로 863 5층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.gymflix.co.kr</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>251</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>580</v>
+      </c>
+      <c r="R66" t="n">
+        <v>831</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
         <is>
           <t>1401898995</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1401898995</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>국민피티 침산점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>kukminpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1398-9797</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kukminpt</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>701</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1008</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1709</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1636758988</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1636758988</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>hannover_reha@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1378-5757</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>대구광역시 중구 공평로8길 11-1 3층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://hanover.co.kr</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>418</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2089</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2507</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1113071233</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1113071233</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>베이앤짐</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>js_healthcare@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1451-4991</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 현풍읍 비슬로 644 베이앤짐</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bai_gym_ai</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>4</v>
+      </c>
+      <c r="R69" t="n">
+        <v>5</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2063998179</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2063998179</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>임팩트 화원점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>tobe1501@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1353-1503</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 화원읍 비슬로 2494 세영빌딩 3층 ' 임팩트 화원점 '</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tobe1501</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>44</v>
+      </c>
+      <c r="R70" t="n">
+        <v>155</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1273389938</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1273389938</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>짐플릭스 세천점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>gymflix_13@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1437-1973</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 세천남로 8 3층 304~308호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.gymflix.co.kr</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>294</v>
+      </c>
+      <c r="R71" t="n">
+        <v>315</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2010307051</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2010307051</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>유달리짐</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>bloomingjeju@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1438-1182</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 논공읍 논공로5길 113 2층 유달리짐</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/udally_gym</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>2</v>
+      </c>
+      <c r="R72" t="n">
+        <v>9</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1697336145</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1697336145</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>댓츠피티</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>thats_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 다사로 23 3층 댓츠피티</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thats_pt</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>9</v>
+      </c>
+      <c r="R73" t="n">
+        <v>12</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1288506358</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1288506358</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>바른운동스튜디오</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>rlawjdgh2848@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1351-0359</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 24 3층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pt_right/</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>6</v>
+      </c>
+      <c r="R74" t="n">
+        <v>132</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1706630598</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1706630598</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>피지컬박스 재활센터,재활PT,선수PT,다이어트,체형교정</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>r2besc@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1324-9527</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 다사읍 다사로 71 201동 A 103호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>62</v>
+      </c>
+      <c r="R75" t="n">
+        <v>160</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1454508250</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1454508250</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>희유핏&amp;필라테스 현풍점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>heeupila@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1437-9976</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 애비뉴스완 상가 3층 3005호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://litt.ly/heeu_fit</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>17</v>
+      </c>
+      <c r="R76" t="n">
+        <v>52</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>2004979603</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2004979603</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/달성군_헬스장.xlsx
+++ b/naver-place-crawler/results_health/달성군_헬스장.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>포에버 짐 화원점</t>
+          <t>귀빈헬스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4evergym@naver.com</t>
+          <t>dy0655@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1307-6093</t>
+          <t>053-593-2555</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 성화로4길 11 2층,3층</t>
+          <t>대구광역시 달성군 다사읍 대실역북로 9 7층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/4evergym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>178</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>233</v>
+        <v>35</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1747875122</t>
+          <t>21311111</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747875122</t>
+          <t>https://m.place.naver.com/place/21311111</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>세천스파헬스&amp;PT</t>
+          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>schealth_spa@naver.com</t>
+          <t>atmhjqnib@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1429-1180</t>
+          <t>0507-1341-2034</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천로 108 5층 헬스장</t>
+          <t>대구광역시 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tailorgym_secheonspa/</t>
+          <t>https://blog.naver.com/atmhjqnib</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>115</v>
+        <v>1193</v>
       </c>
       <c r="Q4" t="n">
-        <v>81</v>
+        <v>557</v>
       </c>
       <c r="R4" t="n">
-        <v>196</v>
+        <v>1750</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2062944785</t>
+          <t>671730517</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2062944785</t>
+          <t>https://m.place.naver.com/place/671730517</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>동아짐 헬스&amp;PT 현풍점</t>
+          <t>스마일피티</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dong_a_gym@naver.com</t>
+          <t>lionajing@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1391-7710</t>
+          <t>0507-1387-9314</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노중앙대로 243 401호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 866 C&amp;B타워 6층 스마일피티</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dong_a_gym</t>
+          <t>https://www.instagram.com/smilept_cap/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2031706267</t>
+          <t>1546368872</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031706267</t>
+          <t>https://m.place.naver.com/place/1546368872</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>한샘사우나헬스</t>
+          <t>다짐휘트니스 대곡점/1:1PT/GX수업/운동프로그램지도</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dutmdgns0402@naver.com</t>
+          <t>dagym_daegok@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>053-551-8888</t>
+          <t>053-634-1414</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 명천로 257</t>
+          <t>대구광역시 달성군 화원읍 비슬로 2727 4층 다짐휘트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dagym_daegok</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>72</v>
+        <v>558</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>79</v>
+        <v>585</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>16131730</t>
+          <t>37989679</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16131730</t>
+          <t>https://m.place.naver.com/place/37989679</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>망고짐</t>
+          <t>옥포서한이다음휘트니스센터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mango_gym@naver.com</t>
+          <t>topten0@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1326-6177</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 52 6층</t>
+          <t>대구광역시 달성군 옥포읍 돌미로6길 5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mang.go55?igsh=cmtuc3ltY3R5dnpq</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1062,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1087,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1899621515</t>
+          <t>1480559305</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899621515</t>
+          <t>https://m.place.naver.com/place/1480559305</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1128,25 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>그린월드헬스클럽</t>
+          <t>짐 엘리트 대실역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hunkyle0104@naver.com</t>
+          <t>gym_b@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1417-4477</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 비슬로530길 29-15</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 874 A동 3층 짐 엘리트 대실역점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gym_b/224238759740</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>269</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>423</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>692</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>16206947</t>
+          <t>520470643</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16206947</t>
+          <t>https://m.place.naver.com/place/520470643</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>패러다임짐 PT 현풍테크노점</t>
+          <t>제이에스짐앤스파</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>paradigm999@naver.com</t>
+          <t>jsgym2020@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1484-7281</t>
+          <t>0507-1338-5512</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노공원로 59 4층, 패러다임짐 현풍테크노점</t>
+          <t>대구광역시 달성군 현풍읍 현풍중앙로14길 71 제이에스짐앤스파</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/paradigmgym_hp</t>
+          <t>https://blog.naver.com/jsgym2020</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="Q9" t="n">
-        <v>145</v>
+        <v>332</v>
       </c>
       <c r="R9" t="n">
-        <v>234</v>
+        <v>380</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1296586077</t>
+          <t>1249711626</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296586077</t>
+          <t>https://m.place.naver.com/place/1249711626</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1312,25 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헬스브로짐&amp;PT 대실역점</t>
+          <t>JJ짐 다사 대실역점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>key_happy@naver.com</t>
+          <t>sjk2948@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1329-4566</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 859 8층</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 873 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/health_brogym_daesil</t>
+          <t>https://blog.naver.com/sjk2948</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1345,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="Q10" t="n">
-        <v>288</v>
+        <v>154</v>
       </c>
       <c r="R10" t="n">
-        <v>523</v>
+        <v>406</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1736955282</t>
+          <t>1377099587</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1736955282</t>
+          <t>https://m.place.naver.com/place/1377099587</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1402,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스마일피티</t>
+          <t>패러다임짐 헬스&amp;PT 다사서재점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lionajing@naver.com</t>
+          <t>paradigm22@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1387-9314</t>
+          <t>0507-1446-8272</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 866 C&amp;B타워 6층 스마일피티</t>
+          <t>대구광역시 달성군 다사읍 서재로 144 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/smilept_cap/</t>
+          <t>https://blog.naver.com/paradigm22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1439,7 +1443,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1459,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="R11" t="n">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,47 +1478,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1546368872</t>
+          <t>1848019910</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546368872</t>
+          <t>https://m.place.naver.com/place/1848019910</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>동아헬스</t>
+          <t>와이짐 구지점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kht8kht@naver.com</t>
+          <t>gym-y3@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1403-9903</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 논공읍 논공로 749 6층 동아헬스</t>
+          <t>대구광역시 달성군 구지면 국가산단대로42길 5-23 6층 와이짐 구지점</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gym-y3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1524,12 +1532,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1545,17 +1553,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="R12" t="n">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1706569605</t>
+          <t>1037912613</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1706569605</t>
+          <t>https://m.place.naver.com/place/1037912613</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1594,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>와이짐 구지점</t>
+          <t>AGYM헬스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gym-y3@naver.com</t>
+          <t>agym_11@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1403-9903</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 국가산단대로42길 5-23 6층 와이짐 구지점</t>
+          <t>대구광역시 달성군 구지면 과학마을로5길 35</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gym-y3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1618,12 +1622,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1639,17 +1643,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1037912613</t>
+          <t>1906219799</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037912613</t>
+          <t>https://m.place.naver.com/place/1906219799</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1680,29 +1684,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>세천케어짐PT샵</t>
+          <t>헬스브로짐&amp;PT 대실역점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>caregym_@naver.com</t>
+          <t>key_happy@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1349-6648</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천북로 7 4층</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 859 8층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/caregym_</t>
+          <t>https://www.instagram.com/health_brogym_daesil</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="Q14" t="n">
-        <v>150</v>
+        <v>288</v>
       </c>
       <c r="R14" t="n">
-        <v>307</v>
+        <v>522</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,51 +1752,47 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1858573540</t>
+          <t>1736955282</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1858573540</t>
+          <t>https://m.place.naver.com/place/1736955282</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>헬스용품</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>여성전용 그룹PT 크롭핏 다사점</t>
+          <t>제이에스헬스케어</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gnstjqdl1234@naver.com</t>
+          <t>jshealth0312@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1366-4795</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로1길 5-1 죽곡메디힐빌딩 7층 여성전용 그룹PT 크롭핏</t>
+          <t>대구광역시 달성군 현풍읍 비슬로 644 제이에스헬스케어</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gnstjqdl1234</t>
+          <t>https://smartstore.naver.com/cwheallthcare</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1811,7 +1807,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1831,13 +1827,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>290</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="R15" t="n">
-        <v>515</v>
+        <v>131</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1842,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1403050690</t>
+          <t>1947032802</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1403050690</t>
+          <t>https://m.place.naver.com/place/1947032802</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1868,29 +1864,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>더바디스쿨 화원점</t>
+          <t>비슬산게르마늄스파</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>thebodyschool_hwawon@naver.com</t>
+          <t>bsm5055@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>053-635-0812</t>
+          <t>053-566-5000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 비슬로 2616</t>
+          <t>대구광역시 달성군 유가읍 테크노순환로12길 4</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thebodyschool_hwawon</t>
+          <t>https://blog.naver.com/bsm5055</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1925,13 +1921,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>65</v>
+        <v>189</v>
       </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="R16" t="n">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,17 +1936,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1939140331</t>
+          <t>488162588</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1939140331</t>
+          <t>https://m.place.naver.com/place/488162588</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1962,29 +1958,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>레드짐 현풍점 헬스&amp;PT</t>
+          <t>플레이짐&amp;PT 현풍점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>redgym114@naver.com</t>
+          <t>playgym_hp@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1437-2268</t>
+          <t>0507-1484-0679</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 26 8층</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 34 601, 604호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/redgym_fit</t>
+          <t>https://blog.naver.com/playgym_hp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1999,7 +1995,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2010,7 +2006,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2019,13 +2015,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="Q17" t="n">
-        <v>307</v>
+        <v>163</v>
       </c>
       <c r="R17" t="n">
-        <v>572</v>
+        <v>387</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2030,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1621391509</t>
+          <t>1567754721</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1621391509</t>
+          <t>https://m.place.naver.com/place/1567754721</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2056,40 +2052,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>호석</t>
+          <t>플레이짐&amp;Pt현풍유가점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ydy5061@naver.com</t>
+          <t>kingfitnessgym@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>053-617-4705</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천로 108</t>
+          <t>대구광역시 달성군 유가읍 테크노공원로 65 5층 플레이&amp;PT 현풍유가점</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/king_korea_2021</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2105,17 +2105,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>645</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2124,17 +2124,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1465682374</t>
+          <t>1614066731</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1465682374</t>
+          <t>https://m.place.naver.com/place/1614066731</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2146,29 +2146,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>reset20 EMS studio</t>
+          <t>바디컷피티샵 현풍</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rugbyyy07@naver.com</t>
+          <t>bodycut-@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1427-0322</t>
+          <t>0507-1357-3856</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 성화로 14</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 34 1동 3층 301호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bodycut-</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>259</v>
       </c>
       <c r="R19" t="n">
-        <v>7</v>
+        <v>314</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2218,17 +2218,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>118041027</t>
+          <t>1642240188</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/118041027</t>
+          <t>https://m.place.naver.com/place/1642240188</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2240,29 +2240,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>피트온24 중동점</t>
+          <t>크로스핏 이공</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>fiton24_jd@naver.com</t>
+          <t>crossfit20tr@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1395-8629</t>
+          <t>0507-1322-5663</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 수성로 212 광원빌딩 3층 피트온24 중동점</t>
+          <t>대구광역시 달성군 다사읍 다사로4길 8 크로스핏20</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fiton24_jd</t>
+          <t>https://www.instagram.com/crossfit20tr/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2288,7 +2288,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1620</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>785</v>
+        <v>123</v>
       </c>
       <c r="R20" t="n">
-        <v>2405</v>
+        <v>133</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,17 +2312,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1472735445</t>
+          <t>1615243167</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472735445</t>
+          <t>https://m.place.naver.com/place/1615243167</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2334,29 +2334,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>053짐 대실역점 헬스&amp;PT</t>
+          <t>피크짐 화원점 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>shutupsquat@naver.com</t>
+          <t>peakgym2022@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1347-0243</t>
+          <t>0507-1446-6339</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로1길 29-9 2층</t>
+          <t>대구광역시 달성군 화원읍 사문진로 441 4층, 5층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_RTxeHs/chat</t>
+          <t>https://litt.ly/peakgym</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2382,22 +2382,22 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>212</v>
+        <v>77</v>
       </c>
       <c r="Q21" t="n">
-        <v>166</v>
+        <v>23</v>
       </c>
       <c r="R21" t="n">
-        <v>378</v>
+        <v>100</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,17 +2406,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1050863472</t>
+          <t>1304504873</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050863472</t>
+          <t>https://m.place.naver.com/place/1304504873</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2428,29 +2428,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>뷰티니스짐 현풍테크노점</t>
+          <t>reset20 EMS studio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>technogym1@naver.com</t>
+          <t>rugbyyy07@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1411-9684</t>
+          <t>0507-1427-0322</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로 254 9층</t>
+          <t>대구광역시 달성군 화원읍 성화로 14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/technogym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>858</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1128</v>
+        <v>6</v>
       </c>
       <c r="R22" t="n">
-        <v>1986</v>
+        <v>7</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,34 +2500,34 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>38648253</t>
+          <t>118041027</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648253</t>
+          <t>https://m.place.naver.com/place/118041027</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>헬스용품</t>
+          <t>부속건물</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>제이에스헬스케어</t>
+          <t>달성군여성문화복지센터수영헬스장</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jshealth0312@naver.com</t>
+          <t>radman99@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2535,12 +2535,12 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 비슬로 644 제이에스헬스케어</t>
+          <t>대구광역시 달성군 화원읍 성천로 5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/cwheallthcare</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="R23" t="n">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2590,17 +2590,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1947032802</t>
+          <t>19637848</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1947032802</t>
+          <t>https://m.place.naver.com/place/19637848</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2612,29 +2612,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>제이에스짐앤스파</t>
+          <t>동아짐 헬스&amp;PT 현풍점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jsgym2020@naver.com</t>
+          <t>dong_a_gym@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1338-5512</t>
+          <t>0507-1391-7710</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 현풍중앙로14길 71 제이에스짐앤스파</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로 243 401호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jsgym2020</t>
+          <t>https://blog.naver.com/dong_a_gym</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2669,13 +2669,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Q24" t="n">
-        <v>332</v>
+        <v>27</v>
       </c>
       <c r="R24" t="n">
-        <v>380</v>
+        <v>78</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2684,17 +2684,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1249711626</t>
+          <t>2031706267</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1249711626</t>
+          <t>https://m.place.naver.com/place/2031706267</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2706,34 +2706,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>다짐휘트니스 대곡점/1:1PT/GX수업/운동프로그램지도</t>
+          <t>더디어짐 헬스&amp;PT 현풍점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dagym_daegok@naver.com</t>
+          <t>the_deergym@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>053-634-1414</t>
+          <t>0507-1390-9558</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 비슬로 2727 4층 다짐휘트니스</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 48 10층 1001호, 1002호, 1003호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dagym_daegok</t>
+          <t>https://thedeargym.homebuilder.co.kr/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>558</v>
+        <v>282</v>
       </c>
       <c r="Q25" t="n">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="R25" t="n">
-        <v>585</v>
+        <v>406</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2778,17 +2778,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>37989679</t>
+          <t>1844851101</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37989679</t>
+          <t>https://m.place.naver.com/place/1844851101</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2800,29 +2800,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>스톤짐 남산점</t>
+          <t>레드짐 현풍2호점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nb99022@naver.com</t>
+          <t>defertoneminem@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>053-424-4001</t>
+          <t>0507-1431-2318</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대구광역시 중구 달구벌대로 2012 13층 (11, 13, 14층)</t>
+          <t>대구광역시 달성군 유가읍 테크노상업로4길 17-9 3층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/stonegym_namsan</t>
+          <t>https://www.instagram.com/redgym_yg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="Q26" t="n">
-        <v>86</v>
+        <v>230</v>
       </c>
       <c r="R26" t="n">
-        <v>376</v>
+        <v>540</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2872,17 +2872,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2027766732</t>
+          <t>1274922467</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2027766732</t>
+          <t>https://m.place.naver.com/place/1274922467</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2894,34 +2894,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>피트온24 범어점</t>
+          <t>053짐 대실역점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fiton24_beomeo@naver.com</t>
+          <t>shutupsquat@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>053-759-3166</t>
+          <t>0507-1347-0243</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 범어천로 214 더리브 503-507호</t>
+          <t>대구광역시 달성군 다사읍 대실역북로1길 29-9 2층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fiton24_beomeo</t>
+          <t>http://pf.kakao.com/_RTxeHs/chat</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2942,7 +2942,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2339</v>
+        <v>212</v>
       </c>
       <c r="Q27" t="n">
-        <v>986</v>
+        <v>166</v>
       </c>
       <c r="R27" t="n">
-        <v>3325</v>
+        <v>378</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2966,17 +2966,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1328042225</t>
+          <t>1050863472</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328042225</t>
+          <t>https://m.place.naver.com/place/1050863472</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2988,29 +2988,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>플레이짐&amp;PT 현풍점</t>
+          <t>테크노폴리스화성파크드림피트니스센터</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>playgym_hp@naver.com</t>
+          <t>anheesang1985@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0507-1484-0679</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 34 601, 604호</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 165</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/playgym_hp</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3020,12 +3016,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3036,22 +3032,22 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>387</v>
+        <v>3</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3060,17 +3056,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1567754721</t>
+          <t>818202311</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1567754721</t>
+          <t>https://m.place.naver.com/place/818202311</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3082,29 +3078,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>여성 맞춤형 헬스&amp;PT 비벨라핏 다사 대실역점</t>
+          <t>행복마당</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>doldol5311573@naver.com</t>
+          <t>happyseogu@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1353-5294</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 880 대실빌딩 3층 여성전용피트니스 비벨라핏 다사점</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 68</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/b.bellafit_daesil/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3114,7 +3106,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3135,17 +3127,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3154,17 +3146,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1548249227</t>
+          <t>1846649632</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548249227</t>
+          <t>https://m.place.naver.com/place/1846649632</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3176,29 +3168,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>레드짐 서재점</t>
+          <t>더바디스쿨 화원점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>redgym_seojae@naver.com</t>
+          <t>thebodyschool_hwawon@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1338-2445</t>
+          <t>053-635-0812</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로 31 3~4층</t>
+          <t>대구광역시 달성군 화원읍 비슬로 2616</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/redgym_seojae</t>
+          <t>https://blog.naver.com/thebodyschool_hwawon</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3233,13 +3225,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>122</v>
+        <v>65</v>
       </c>
       <c r="Q30" t="n">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="R30" t="n">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,34 +3240,34 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2048462768</t>
+          <t>1939140331</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2048462768</t>
+          <t>https://m.place.naver.com/place/1939140331</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>공유누리 개방자원</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>행복마당</t>
+          <t>다사읍주민자치센터 본관2층(헬스장)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>happyseogu@naver.com</t>
+          <t>reminisce_bin@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -3283,7 +3275,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 68</t>
+          <t>대구광역시 달성군 다사읍 매곡로12길 37 다사읍주민자치센터 본관2층 헬스장</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3323,13 +3315,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,17 +3330,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1846649632</t>
+          <t>1824150538</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1846649632</t>
+          <t>https://m.place.naver.com/place/1824150538</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3360,29 +3352,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>웰휘트니스24h 다사서재점</t>
+          <t>세천케어짐PT샵</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>tjql23@naver.com</t>
+          <t>caregym_@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1347-9665</t>
+          <t>0507-1349-6648</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로 121 4층</t>
+          <t>대구광역시 달성군 다사읍 세천북로 7 4층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjql23</t>
+          <t>https://blog.naver.com/caregym_</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3417,13 +3409,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="Q32" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="R32" t="n">
-        <v>132</v>
+        <v>307</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,17 +3424,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1161171342</t>
+          <t>1858573540</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161171342</t>
+          <t>https://m.place.naver.com/place/1858573540</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3454,29 +3446,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>다빠짐&amp;죠아짐</t>
+          <t>새롬사우나 헬스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>joagym1@naver.com</t>
+          <t>topten0@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1472-6488</t>
+          <t>053-638-4386</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로174길 15 명륜진사갈비 3층</t>
+          <t>대구광역시 달성군 화원읍 비슬로 2508</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/joagym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3486,12 +3478,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3507,17 +3499,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>143</v>
+        <v>4</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,17 +3518,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1468896867</t>
+          <t>16130959</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468896867</t>
+          <t>https://m.place.naver.com/place/16130959</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3548,29 +3540,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>레드짐 현풍2호점 헬스&amp;PT</t>
+          <t>여성 맞춤형 헬스&amp;PT 비벨라핏 다사 대실역점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>defertoneminem@naver.com</t>
+          <t>doldol5311573@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1431-2318</t>
+          <t>0507-1353-5294</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노상업로4길 17-9 3층</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 880 대실빌딩 3층 여성전용피트니스 비벨라핏 다사점</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/redgym_yg</t>
+          <t>https://www.instagram.com/b.bellafit_daesil/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3605,13 +3597,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>305</v>
+        <v>477</v>
       </c>
       <c r="Q34" t="n">
-        <v>229</v>
+        <v>350</v>
       </c>
       <c r="R34" t="n">
-        <v>534</v>
+        <v>827</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3620,17 +3612,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1274922467</t>
+          <t>1548249227</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274922467</t>
+          <t>https://m.place.naver.com/place/1548249227</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3642,29 +3634,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JJ짐 다사 대실역점 헬스 PT</t>
+          <t>레드짐 동성로점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sjk2948@naver.com</t>
+          <t>redgym_dongseongro@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0507-1329-4566</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 873 5층</t>
+          <t>대구광역시 중구 동성로2길 95 지하1, 2층 B101, B201호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sjk2948</t>
+          <t>https://www.instagram.com/redgym_dongseongro</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3679,7 +3667,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3699,13 +3687,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
       <c r="Q35" t="n">
-        <v>154</v>
+        <v>393</v>
       </c>
       <c r="R35" t="n">
-        <v>406</v>
+        <v>788</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3714,51 +3702,51 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1377099587</t>
+          <t>1444163779</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377099587</t>
+          <t>https://m.place.naver.com/place/1444163779</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>헬스위드짐</t>
+          <t>세천스파헬스&amp;PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>hjya0119@naver.com</t>
+          <t>schealth_spa@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1309-5393</t>
+          <t>0507-1429-1180</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노상업로4길 17-9 4층</t>
+          <t>대구광역시 달성군 다사읍 세천로 108 5층 헬스장</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hjya0119</t>
+          <t>https://www.instagram.com/tailorgym_secheonspa/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3773,7 +3761,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3793,13 +3781,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="Q36" t="n">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="R36" t="n">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3808,17 +3796,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1700394540</t>
+          <t>2062944785</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700394540</t>
+          <t>https://m.place.naver.com/place/2062944785</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3830,29 +3818,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>바디컷피티샵 현풍</t>
+          <t>레드짐 현풍점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>bodycut-@naver.com</t>
+          <t>redgym114@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1357-3856</t>
+          <t>0507-1437-2268</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 34 1동 3층 301호</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 26 8층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodycut-</t>
+          <t>https://www.instagram.com/redgym_fit</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3867,7 +3855,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3883,17 +3871,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>55</v>
+        <v>266</v>
       </c>
       <c r="Q37" t="n">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="R37" t="n">
-        <v>314</v>
+        <v>573</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,17 +3890,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1642240188</t>
+          <t>1621391509</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1642240188</t>
+          <t>https://m.place.naver.com/place/1621391509</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3924,44 +3912,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>선샤인 사우나 헬스</t>
+          <t>패러다임짐 PT 현풍테크노점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>yoon766@naver.com</t>
+          <t>paradigm999@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>053-587-0035</t>
+          <t>0507-1484-7281</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로2길 8-6</t>
+          <t>대구광역시 달성군 유가읍 테크노공원로 59 4층, 패러다임짐 현풍테크노점</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/paradigmgym_hp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3977,17 +3965,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>310</v>
+        <v>89</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="R38" t="n">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,17 +3984,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>38415528</t>
+          <t>1296586077</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38415528</t>
+          <t>https://m.place.naver.com/place/1296586077</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4018,29 +4006,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>플레이짐&amp;Pt현풍유가점</t>
+          <t>망고짐</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kingfitnessgym@naver.com</t>
+          <t>mango_gym@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>053-617-4705</t>
+          <t>0507-1326-6177</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노공원로 65 5층 플레이&amp;PT 현풍유가점</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 52 6층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/king_korea_2021</t>
+          <t>https://www.instagram.com/mang.go55?igsh=cmtuc3ltY3R5dnpq</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4075,13 +4063,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>219</v>
+        <v>6</v>
       </c>
       <c r="Q39" t="n">
-        <v>426</v>
+        <v>12</v>
       </c>
       <c r="R39" t="n">
-        <v>645</v>
+        <v>18</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4090,17 +4078,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1614066731</t>
+          <t>1899621515</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614066731</t>
+          <t>https://m.place.naver.com/place/1899621515</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4112,39 +4100,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>피크짐 화원점 헬스 &amp; PT</t>
+          <t>선샤인 사우나 헬스</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>peakgym2022@naver.com</t>
+          <t>yoon766@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1446-6339</t>
+          <t>053-587-0035</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 사문진로 441 4층, 5층</t>
+          <t>대구광역시 달성군 다사읍 대실역북로2길 8-6</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://litt.ly/peakgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4169,13 +4157,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>77</v>
+        <v>310</v>
       </c>
       <c r="Q40" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>100</v>
+        <v>310</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4184,17 +4172,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1304504873</t>
+          <t>38415528</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1304504873</t>
+          <t>https://m.place.naver.com/place/38415528</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4206,29 +4194,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>디젤피트니스</t>
+          <t>스톤짐 남산점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dieseldaegok@naver.com</t>
+          <t>nb99022@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1303-0976</t>
+          <t>053-424-4001</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미상업로1길 2 화인탑메디컬빌딩 7층 디젤피트니스</t>
+          <t>대구광역시 중구 달구벌대로 2012 13층 (11, 13, 14층)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/stonegym_namsan</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4238,7 +4226,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4259,17 +4247,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>150</v>
+        <v>291</v>
       </c>
       <c r="Q41" t="n">
-        <v>241</v>
+        <v>88</v>
       </c>
       <c r="R41" t="n">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4278,51 +4266,51 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1888886298</t>
+          <t>2027766732</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1888886298</t>
+          <t>https://m.place.naver.com/place/2027766732</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>새롬사우나 헬스</t>
+          <t>헬스위드짐</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>hjya0119@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>053-638-4386</t>
+          <t>0507-1309-5393</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 비슬로 2508</t>
+          <t>대구광역시 달성군 유가읍 테크노상업로4길 17-9 4층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/hjya0119</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4332,12 +4320,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4353,17 +4341,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="R42" t="n">
-        <v>4</v>
+        <v>134</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4372,17 +4360,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>16130959</t>
+          <t>1700394540</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16130959</t>
+          <t>https://m.place.naver.com/place/1700394540</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4394,25 +4382,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>서재헬스</t>
+          <t>디젤피트니스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>seojaehealth@naver.com</t>
+          <t>dieseldaegok@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1303-0976</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로 141 서재헬스</t>
+          <t>대구광역시 달성군 옥포읍 돌미상업로1길 2 화인탑메디컬빌딩 7층 디젤피트니스</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/seojaehealth</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4422,12 +4414,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4447,13 +4439,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="Q43" t="n">
-        <v>7</v>
+        <v>241</v>
       </c>
       <c r="R43" t="n">
-        <v>18</v>
+        <v>391</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4462,46 +4454,42 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1159781373</t>
+          <t>1888886298</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159781373</t>
+          <t>https://m.place.naver.com/place/1888886298</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>귀빈헬스</t>
+          <t>동아헬스</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>dy0655@naver.com</t>
+          <t>kht8kht@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>053-593-2555</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로 9 7층</t>
+          <t>대구광역시 달성군 논공읍 논공로 749 6층 동아헬스</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4541,13 +4529,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R44" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,17 +4544,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>21311111</t>
+          <t>1706569605</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21311111</t>
+          <t>https://m.place.naver.com/place/1706569605</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4660,7 +4648,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4672,34 +4660,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 수성점</t>
+          <t>피트온24 중동점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>chl3503@naver.com</t>
+          <t>fiton24_jd@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1491-7677</t>
+          <t>0507-1395-8629</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 청수로26길 36 한성스퀘어 5층</t>
+          <t>대구광역시 수성구 수성로 212 광원빌딩 3층 피트온24 중동점</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://boddy.imweb.me/</t>
+          <t>https://blog.naver.com/fiton24_jd</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4729,13 +4717,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>945</v>
+        <v>1621</v>
       </c>
       <c r="Q46" t="n">
-        <v>1344</v>
+        <v>804</v>
       </c>
       <c r="R46" t="n">
-        <v>2289</v>
+        <v>2425</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4744,17 +4732,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1885094891</t>
+          <t>1472735445</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885094891</t>
+          <t>https://m.place.naver.com/place/1472735445</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4766,29 +4754,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>크로스핏 이공</t>
+          <t>파워헬스클럽</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>crossfit20tr@naver.com</t>
+          <t>power2963805@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0507-1322-5663</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 다사로4길 8 크로스핏20</t>
+          <t>대구광역시 달성군 화원읍 비슬로 2697</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit20tr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4798,7 +4782,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4814,22 +4798,22 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="n">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>133</v>
+        <v>5</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4838,17 +4822,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1615243167</t>
+          <t>1475412010</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1615243167</t>
+          <t>https://m.place.naver.com/place/1475412010</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4860,12 +4844,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AGYM헬스</t>
+          <t>서재헬스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>agym_11@naver.com</t>
+          <t>seojaehealth@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4873,12 +4857,12 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로5길 35</t>
+          <t>대구광역시 달성군 다사읍 서재로 141 서재헬스</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/seojaehealth</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4888,12 +4872,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4913,13 +4897,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4928,17 +4912,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1906219799</t>
+          <t>1159781373</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906219799</t>
+          <t>https://m.place.naver.com/place/1159781373</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4934,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>테크노폴리스화성파크드림피트니스센터</t>
+          <t>호석</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>anheesang1985@naver.com</t>
+          <t>ydy5061@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4963,7 +4947,7 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 165</t>
+          <t>대구광역시 달성군 다사읍 세천로 108</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5003,13 +4987,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5018,47 +5002,51 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>818202311</t>
+          <t>1465682374</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/818202311</t>
+          <t>https://m.place.naver.com/place/1465682374</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>공유누리 개방자원</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>다사읍주민자치센터 본관2층(헬스장)</t>
+          <t>헬스&amp;PT 몰리짐 장기점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ulju_love@naver.com</t>
+          <t>mollygym_vol3@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1469-9682</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 매곡로12길 37 다사읍주민자치센터 본관2층 헬스장</t>
+          <t>대구광역시 달서구 용산로 80 에이동</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mollygym_vol.3/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5068,7 +5056,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5089,17 +5077,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>1063</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>545</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>1608</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5108,17 +5096,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1824150538</t>
+          <t>1048460846</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824150538</t>
+          <t>https://m.place.naver.com/place/1048460846</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5130,29 +5118,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>비슬산게르마늄스파</t>
+          <t>다빠짐&amp;죠아짐</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>bsm5055@naver.com</t>
+          <t>joagym1@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>053-566-5000</t>
+          <t>0507-1472-6488</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노순환로12길 4</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 15 명륜진사갈비 3층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bsm5055</t>
+          <t>https://blog.naver.com/joagym1</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5187,13 +5175,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>189</v>
+        <v>8</v>
       </c>
       <c r="Q51" t="n">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="R51" t="n">
-        <v>417</v>
+        <v>143</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5202,17 +5190,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>488162588</t>
+          <t>1468896867</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/488162588</t>
+          <t>https://m.place.naver.com/place/1468896867</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5224,29 +5212,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>짐 엘리트 대실역점</t>
+          <t>뷰티니스짐 현풍테크노점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>gym_b@naver.com</t>
+          <t>technogym1@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1417-4477</t>
+          <t>0507-1411-9684</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 874 A동 3층 짐 엘리트 대실역점</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로 254 9층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gym_b/224238759740</t>
+          <t>https://blog.naver.com/technogym1</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5281,13 +5269,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>269</v>
+        <v>862</v>
       </c>
       <c r="Q52" t="n">
-        <v>423</v>
+        <v>1128</v>
       </c>
       <c r="R52" t="n">
-        <v>692</v>
+        <v>1990</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5296,17 +5284,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>520470643</t>
+          <t>38648253</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/520470643</t>
+          <t>https://m.place.naver.com/place/38648253</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5318,29 +5306,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
+          <t>현풍 하이그룹피티 &amp; 찌지다</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>atmhjqnib@naver.com</t>
+          <t>topten0@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1341-2034</t>
+          <t>0507-1347-3429</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 50 제이앤비빌딩 5층 501호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/atmhjqnib</t>
+          <t>https://www.instagram.com/invites/contact/?i=1amokd5vtp2ir&amp;utm_content=mvgw8cs</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5355,7 +5343,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5375,13 +5363,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1193</v>
+        <v>35</v>
       </c>
       <c r="Q53" t="n">
-        <v>558</v>
+        <v>140</v>
       </c>
       <c r="R53" t="n">
-        <v>1751</v>
+        <v>175</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5390,17 +5378,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>671730517</t>
+          <t>1807496277</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/671730517</t>
+          <t>https://m.place.naver.com/place/1807496277</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5412,29 +5400,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>나우휘트니스클럽</t>
+          <t>피트온24 범어점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kns3791@naver.com</t>
+          <t>fiton24_beomeo@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>053-614-0255</t>
+          <t>053-759-3166</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 논공읍 논공로5길 229</t>
+          <t>대구광역시 수성구 범어천로 214 더리브 503-507호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/fiton24_beomeo</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5444,7 +5432,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5465,17 +5453,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2340</v>
       </c>
       <c r="Q54" t="n">
-        <v>2</v>
+        <v>989</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>3329</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5484,17 +5472,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>16135809</t>
+          <t>1328042225</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16135809</t>
+          <t>https://m.place.naver.com/place/1328042225</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5506,34 +5494,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>더디어짐 헬스&amp;PT 현풍점</t>
+          <t>레드짐 서재점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>the_deergym@naver.com</t>
+          <t>redgym_seojae@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1390-9558</t>
+          <t>0507-1338-2445</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 48 10층 1001호, 1002호, 1003호</t>
+          <t>대구광역시 달성군 다사읍 서재로 31 3~4층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://thedeargym.homebuilder.co.kr/</t>
+          <t>https://blog.naver.com/redgym_seojae</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5543,7 +5531,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5563,13 +5551,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>282</v>
+        <v>122</v>
       </c>
       <c r="Q55" t="n">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="R55" t="n">
-        <v>405</v>
+        <v>229</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5578,17 +5566,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1844851101</t>
+          <t>2048462768</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1844851101</t>
+          <t>https://m.place.naver.com/place/2048462768</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5600,25 +5588,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>옥포서한이다음휘트니스센터</t>
+          <t>여성전용 그룹PT 크롭핏 다사점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>gnstjqdl1234@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1366-4795</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미로6길 5</t>
+          <t>대구광역시 달성군 다사읍 대실역북로1길 5-1 죽곡메디힐빌딩 7층 여성전용 그룹PT 크롭핏</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gnstjqdl1234</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5628,12 +5620,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5649,17 +5641,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>227</v>
       </c>
       <c r="R56" t="n">
-        <v>3</v>
+        <v>517</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5668,17 +5660,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1480559305</t>
+          <t>1403050690</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1480559305</t>
+          <t>https://m.place.naver.com/place/1403050690</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5690,25 +5682,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>파워헬스클럽</t>
+          <t>포에버 짐 화원점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>power2963805@naver.com</t>
+          <t>4evergym@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1307-6093</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 비슬로 2697</t>
+          <t>대구광역시 달성군 화원읍 성화로4길 11 2층,3층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/4evergym</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5718,12 +5714,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5739,17 +5735,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="R57" t="n">
-        <v>5</v>
+        <v>234</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5758,42 +5754,46 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1475412010</t>
+          <t>1747875122</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1475412010</t>
+          <t>https://m.place.naver.com/place/1747875122</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>부속건물</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>달성군여성문화복지센터수영헬스장</t>
+          <t>한샘사우나헬스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>radman99@naver.com</t>
+          <t>dutmdgns0402@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>053-551-8888</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 성천로 5</t>
+          <t>대구광역시 달성군 화원읍 명천로 257</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5833,13 +5833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="Q58" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="R58" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5848,17 +5848,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>19637848</t>
+          <t>16131730</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19637848</t>
+          <t>https://m.place.naver.com/place/16131730</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5870,29 +5870,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>패러다임짐 헬스&amp;PT 다사서재점</t>
+          <t>웰휘트니스24h 다사서재점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>paradigm22@naver.com</t>
+          <t>tjql23@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1446-8272</t>
+          <t>0507-1347-9665</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로 144 2층</t>
+          <t>대구광역시 달성군 다사읍 서재로 121 4층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/paradigm22</t>
+          <t>https://blog.naver.com/tjql23</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5927,13 +5927,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="Q59" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="R59" t="n">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5942,17 +5942,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1848019910</t>
+          <t>1161171342</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1848019910</t>
+          <t>https://m.place.naver.com/place/1161171342</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5964,44 +5964,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>현풍 하이그룹피티 &amp; 찌지다</t>
+          <t>그린월드헬스클럽</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>hunkyle0104@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1347-3429</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 50 제이앤비빌딩 5층 501호</t>
+          <t>대구광역시 달성군 화원읍 비슬로530길 29-15</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/invites/contact/?i=1amokd5vtp2ir&amp;utm_content=mvgw8cs</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6017,17 +6013,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6036,47 +6032,51 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1807496277</t>
+          <t>16206947</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1807496277</t>
+          <t>https://m.place.naver.com/place/16206947</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>예스점핑다이어트</t>
+          <t>나우휘트니스클럽</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mamihong@naver.com</t>
+          <t>kns3791@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>053-614-0255</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 다사역로 5 4층</t>
+          <t>대구광역시 달성군 논공읍 논공로5길 229</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/yes.jumping</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6107,17 +6107,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" t="n">
-        <v>50</v>
-      </c>
       <c r="R61" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6126,34 +6126,34 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1206224366</t>
+          <t>16135809</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206224366</t>
+          <t>https://m.place.naver.com/place/16135809</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>에프엠트레이닝센터</t>
+          <t>예스점핑다이어트</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>fm_trainingcenter@naver.com</t>
+          <t>mamihong@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -6161,12 +6161,12 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노순환로7길 33 1층</t>
+          <t>대구광역시 달성군 다사읍 다사역로 5 4층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fm_trainingcenter</t>
+          <t>http://www.instagram.com/yes.jumping</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6201,13 +6201,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="R62" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6216,17 +6216,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1843484347</t>
+          <t>1206224366</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843484347</t>
+          <t>https://m.place.naver.com/place/1206224366</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6238,25 +6238,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>크라이오식스</t>
+          <t>에이짐휘트니스</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>tjwls1986@naver.com</t>
+          <t>agymf@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1320-5959</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 성화로 14 2F</t>
+          <t>대구광역시 달성군 구지면 과학마을로5길 35 드림랜드 1층 101호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/cryosix_6</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6266,7 +6270,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6287,17 +6291,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6306,17 +6310,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1375896553</t>
+          <t>1554834015</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1375896553</t>
+          <t>https://m.place.naver.com/place/1554834015</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6328,29 +6332,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>에이짐휘트니스</t>
+          <t>댓츠피티</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>agymf@naver.com</t>
+          <t>thats_pt@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0507-1320-5959</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로5길 35 드림랜드 1층 101호</t>
+          <t>대구광역시 달성군 다사읍 다사로 23 3층 댓츠피티</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/thats_pt</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6381,17 +6381,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R64" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6400,17 +6400,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1554834015</t>
+          <t>1288506358</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1554834015</t>
+          <t>https://m.place.naver.com/place/1288506358</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6422,34 +6422,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>라라그룹피티</t>
+          <t>짐플릭스 세천점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>top85601@naver.com</t>
+          <t>gymflix_13@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1400-0326</t>
+          <t>0507-1437-1973</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역남로 18 3층 304호</t>
+          <t>대구광역시 달성군 다사읍 세천남로 8 3층 304~308호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lala_pt0303</t>
+          <t>https://www.gymflix.co.kr</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6479,13 +6479,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Q65" t="n">
-        <v>53</v>
+        <v>294</v>
       </c>
       <c r="R65" t="n">
-        <v>65</v>
+        <v>315</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6494,17 +6494,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1435201471</t>
+          <t>2010307051</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1435201471</t>
+          <t>https://m.place.naver.com/place/2010307051</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6516,34 +6516,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>짐플릭스 대실역점</t>
+          <t>크라이오식스</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>qo6107@naver.com</t>
+          <t>tjwls1986@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0507-1363-2799</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 863 5층</t>
+          <t>대구광역시 달성군 화원읍 성화로 14 2F</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr</t>
+          <t>http://www.instagram.com/cryosix_6</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6573,13 +6569,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>251</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>580</v>
+        <v>6</v>
       </c>
       <c r="R66" t="n">
-        <v>831</v>
+        <v>8</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6588,17 +6584,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1401898995</t>
+          <t>1375896553</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1401898995</t>
+          <t>https://m.place.naver.com/place/1375896553</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6610,29 +6606,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>국민피티 침산점</t>
+          <t>유달리짐</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kukminpt@naver.com</t>
+          <t>bloomingjeju@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1398-9797</t>
+          <t>0507-1438-1182</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구광역시 달성군 논공읍 논공로5길 113 2층 유달리짐</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kukminpt</t>
+          <t>http://www.instagram.com/udally_gym</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6667,13 +6663,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>701</v>
+        <v>7</v>
       </c>
       <c r="Q67" t="n">
-        <v>1008</v>
+        <v>2</v>
       </c>
       <c r="R67" t="n">
-        <v>1709</v>
+        <v>9</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6682,17 +6678,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1636758988</t>
+          <t>1697336145</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636758988</t>
+          <t>https://m.place.naver.com/place/1697336145</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6704,34 +6700,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+          <t>짐플릭스 대실역점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>hannover_reha@naver.com</t>
+          <t>qo6107@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1378-5757</t>
+          <t>0507-1363-2799</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>대구광역시 중구 공평로8길 11-1 3층</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 863 5층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://hanover.co.kr</t>
+          <t>https://www.gymflix.co.kr</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6761,13 +6757,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>418</v>
+        <v>251</v>
       </c>
       <c r="Q68" t="n">
-        <v>2089</v>
+        <v>580</v>
       </c>
       <c r="R68" t="n">
-        <v>2507</v>
+        <v>831</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6776,17 +6772,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1113071233</t>
+          <t>1401898995</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113071233</t>
+          <t>https://m.place.naver.com/place/1401898995</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6798,29 +6794,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>베이앤짐</t>
+          <t>피지컬박스 재활센터,재활PT,선수PT,다이어트,체형교정</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>js_healthcare@naver.com</t>
+          <t>r2besc@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1451-4991</t>
+          <t>0507-1324-9527</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 비슬로 644 베이앤짐</t>
+          <t>대구광역시 달성군 다사읍 다사로 71 201동 A 103호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bai_gym_ai</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6830,7 +6826,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6851,17 +6847,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="Q69" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="R69" t="n">
-        <v>5</v>
+        <v>159</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6870,17 +6866,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2063998179</t>
+          <t>1454508250</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2063998179</t>
+          <t>https://m.place.naver.com/place/1454508250</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6892,29 +6888,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>임팩트 화원점</t>
+          <t>베이앤짐</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>tobe1501@naver.com</t>
+          <t>js_healthcare@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1353-1503</t>
+          <t>0507-1451-4991</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 비슬로 2494 세영빌딩 3층 ' 임팩트 화원점 '</t>
+          <t>대구광역시 달성군 현풍읍 비슬로 644 베이앤짐</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tobe1501</t>
+          <t>https://www.instagram.com/bai_gym_ai</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6929,7 +6925,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6949,13 +6945,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
-        <v>155</v>
+        <v>5</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6964,17 +6960,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1273389938</t>
+          <t>2063998179</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1273389938</t>
+          <t>https://m.place.naver.com/place/2063998179</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6986,34 +6982,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>짐플릭스 세천점</t>
+          <t>에프엠트레이닝센터</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>gymflix_13@naver.com</t>
+          <t>fm_trainingcenter@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1437-1973</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천남로 8 3층 304~308호</t>
+          <t>대구광역시 달성군 유가읍 테크노순환로7길 33 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr</t>
+          <t>https://blog.naver.com/fm_trainingcenter</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7023,7 +7015,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7043,13 +7035,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="Q71" t="n">
-        <v>294</v>
+        <v>24</v>
       </c>
       <c r="R71" t="n">
-        <v>315</v>
+        <v>84</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7058,17 +7050,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2010307051</t>
+          <t>1843484347</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2010307051</t>
+          <t>https://m.place.naver.com/place/1843484347</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7080,29 +7072,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>유달리짐</t>
+          <t>임팩트 화원점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>bloomingjeju@naver.com</t>
+          <t>tobe1501@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1438-1182</t>
+          <t>0507-1353-1503</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 논공읍 논공로5길 113 2층 유달리짐</t>
+          <t>대구광역시 달성군 화원읍 비슬로 2494 세영빌딩 3층 ' 임팩트 화원점 '</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/udally_gym</t>
+          <t>https://blog.naver.com/tobe1501</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7117,7 +7109,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7137,13 +7129,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="Q72" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="R72" t="n">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7152,17 +7144,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1697336145</t>
+          <t>1273389938</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1697336145</t>
+          <t>https://m.place.naver.com/place/1273389938</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7174,25 +7166,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>댓츠피티</t>
+          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>thats_pt@naver.com</t>
+          <t>hannover_reha@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1378-5757</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 다사로 23 3층 댓츠피티</t>
+          <t>대구광역시 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thats_pt</t>
+          <t>https://hanover.co.kr</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7207,7 +7203,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7227,13 +7223,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3</v>
+        <v>420</v>
       </c>
       <c r="Q73" t="n">
-        <v>9</v>
+        <v>2105</v>
       </c>
       <c r="R73" t="n">
-        <v>12</v>
+        <v>2525</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7242,17 +7238,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1288506358</t>
+          <t>1113071233</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1288506358</t>
+          <t>https://m.place.naver.com/place/1113071233</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7342,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7358,29 +7354,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>피지컬박스 재활센터,재활PT,선수PT,다이어트,체형교정</t>
+          <t>라라그룹피티</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>r2besc@naver.com</t>
+          <t>top85601@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1324-9527</t>
+          <t>0507-1400-0326</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 다사로 71 201동 A 103호</t>
+          <t>대구광역시 달성군 다사읍 대실역남로 18 3층 304호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lala_pt0303</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7390,7 +7386,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7411,17 +7407,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="Q75" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="R75" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7430,17 +7426,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1454508250</t>
+          <t>1435201471</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454508250</t>
+          <t>https://m.place.naver.com/place/1435201471</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7530,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
